--- a/cet4/result/40_重生女帝_权谋天下的逆袭路/40_重生女帝_权谋天下的逆袭路_学习版.xlsx
+++ b/cet4/result/40_重生女帝_权谋天下的逆袭路/40_重生女帝_权谋天下的逆袭路_学习版.xlsx
@@ -397,759 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>roof</v>
       </c>
       <c r="B2" t="str">
-        <v>roof</v>
+        <v>/ruːf/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D2" t="str">
         <v>屋顶</v>
       </c>
-      <c r="D2" t="str">
-        <v>roof(屋顶)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>southwest</v>
       </c>
       <c r="B3" t="str">
-        <v>southwest</v>
+        <v>/ˌsaʊθˈwest/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D3" t="str">
         <v>西南</v>
       </c>
-      <c r="D3" t="str">
-        <v>southwest(西南)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>unexpected</v>
       </c>
       <c r="B4" t="str">
-        <v>unexpected</v>
+        <v>/ˌʌnɪkˈspektɪd/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>意外的</v>
       </c>
-      <c r="D4" t="str">
-        <v>unexpected(意外的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>grace</v>
       </c>
       <c r="B5" t="str">
-        <v>grace</v>
+        <v>/ɡreɪs/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D5" t="str">
         <v>优雅</v>
       </c>
-      <c r="D5" t="str">
-        <v>grace(优雅)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>dock</v>
       </c>
       <c r="B6" t="str">
-        <v>dock</v>
+        <v>/dɑːk/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>码头</v>
       </c>
-      <c r="D6" t="str">
-        <v>dock(码头)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>index</v>
       </c>
       <c r="B7" t="str">
-        <v>index</v>
+        <v>/ˈɪndeks/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>索引</v>
       </c>
-      <c r="D7" t="str">
-        <v>index(索引)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>verify</v>
       </c>
       <c r="B8" t="str">
-        <v>verify</v>
+        <v>/ˈverɪfaɪ/</v>
       </c>
       <c r="C8" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D8" t="str">
         <v>核实</v>
       </c>
-      <c r="D8" t="str">
-        <v>verify(核实)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>applicable</v>
       </c>
       <c r="B9" t="str">
-        <v>applicable</v>
+        <v>/əˈplɪkəbl/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>适用的</v>
       </c>
-      <c r="D9" t="str">
-        <v>applicable(适用的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>swim</v>
       </c>
       <c r="B10" t="str">
-        <v>swim</v>
+        <v>/swɪm/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>游泳</v>
       </c>
-      <c r="D10" t="str">
-        <v>swim(游泳)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>throne</v>
       </c>
       <c r="B11" t="str">
-        <v>throne</v>
+        <v>/θroʊn/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>王座</v>
       </c>
-      <c r="D11" t="str">
-        <v>throne(王座)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>weapon</v>
       </c>
       <c r="B12" t="str">
-        <v>weapon</v>
+        <v>/ˈwepən/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>武器</v>
       </c>
-      <c r="D12" t="str">
-        <v>weapon(武器)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>medium</v>
       </c>
       <c r="B13" t="str">
-        <v>medium</v>
+        <v>/ˈmiːdiəm/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>媒介</v>
       </c>
-      <c r="D13" t="str">
-        <v>medium(媒介)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>element</v>
       </c>
       <c r="B14" t="str">
-        <v>element</v>
+        <v>/ˈelɪmənt/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>元素</v>
       </c>
-      <c r="D14" t="str">
-        <v>element(元素)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>bathroom</v>
       </c>
       <c r="B15" t="str">
-        <v>bathroom</v>
+        <v>/ˈbɑːθruːm/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>浴室</v>
       </c>
-      <c r="D15" t="str">
-        <v>bathroom(浴室)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>position</v>
       </c>
       <c r="B16" t="str">
-        <v>position</v>
+        <v>/pəˈzɪʃn/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D16" t="str">
         <v>职位</v>
       </c>
-      <c r="D16" t="str">
-        <v>position(职位)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>brave</v>
       </c>
       <c r="B17" t="str">
-        <v>brave</v>
+        <v>/breɪv/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>勇敢</v>
       </c>
-      <c r="D17" t="str">
-        <v>brave(勇敢)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>future</v>
       </c>
       <c r="B18" t="str">
-        <v>future</v>
+        <v>/ˈfjuːtʃər/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>未来</v>
       </c>
-      <c r="D18" t="str">
-        <v>future(未来)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>wheel</v>
       </c>
       <c r="B19" t="str">
-        <v>wheel</v>
+        <v>/wiːl/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>轮子</v>
       </c>
-      <c r="D19" t="str">
-        <v>wheel(轮子)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>frank</v>
       </c>
       <c r="B20" t="str">
-        <v>frank</v>
+        <v>/fræŋk/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>坦率的</v>
       </c>
-      <c r="D20" t="str">
-        <v>frank(坦率的)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>clock</v>
       </c>
       <c r="B21" t="str">
-        <v>clock</v>
+        <v>/klɑːk/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D21" t="str">
         <v>时钟</v>
       </c>
-      <c r="D21" t="str">
-        <v>clock(时钟)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>behind</v>
       </c>
       <c r="B22" t="str">
-        <v>behind</v>
+        <v>/bɪˈhaɪnd/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./adv./prep.</v>
+      </c>
+      <c r="D22" t="str">
         <v>后面</v>
       </c>
-      <c r="D22" t="str">
-        <v>behind(后面)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>sudden</v>
       </c>
       <c r="B23" t="str">
-        <v>sudden</v>
+        <v>/ˈsʌdn/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>突然的</v>
       </c>
-      <c r="D23" t="str">
-        <v>sudden(突然的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>our</v>
       </c>
       <c r="B24" t="str">
-        <v>our</v>
+        <v>/ɑːr,ˈaʊər/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D24" t="str">
         <v>我们的</v>
       </c>
-      <c r="D24" t="str">
-        <v>our(我们的)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>dog</v>
       </c>
       <c r="B25" t="str">
-        <v>dog</v>
+        <v>/dɔːɡ/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D25" t="str">
         <v>狗</v>
       </c>
-      <c r="D25" t="str">
-        <v>dog(狗)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>occupy</v>
       </c>
       <c r="B26" t="str">
-        <v>occupy</v>
+        <v>/ˈɑːkjupaɪ/</v>
       </c>
       <c r="C26" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D26" t="str">
         <v>占据</v>
       </c>
-      <c r="D26" t="str">
-        <v>occupy(占据)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>leap</v>
       </c>
       <c r="B27" t="str">
-        <v>leap</v>
+        <v>/liːp/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D27" t="str">
         <v>跳跃</v>
       </c>
-      <c r="D27" t="str">
-        <v>leap(跳跃)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>vitamin</v>
       </c>
       <c r="B28" t="str">
-        <v>vitamin</v>
+        <v>/ˈvaɪtəmɪn/</v>
       </c>
       <c r="C28" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>维生素</v>
       </c>
-      <c r="D28" t="str">
-        <v>vitamin(维生素)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>favour</v>
       </c>
       <c r="B29" t="str">
-        <v>favour</v>
+        <v>/ˈfeɪvər/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D29" t="str">
         <v>恩惠</v>
       </c>
-      <c r="D29" t="str">
-        <v>favour(恩惠)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>strategy</v>
       </c>
       <c r="B30" t="str">
-        <v>strategy</v>
+        <v>/ˈstrætədʒi/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>策略</v>
       </c>
-      <c r="D30" t="str">
-        <v>strategy(策略)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>ear</v>
       </c>
       <c r="B31" t="str">
-        <v>ear</v>
+        <v>/ɪr/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D31" t="str">
         <v>耳朵</v>
       </c>
-      <c r="D31" t="str">
-        <v>ear(耳朵)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>battle</v>
       </c>
       <c r="B32" t="str">
-        <v>battle</v>
+        <v>/ˈbætl/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D32" t="str">
         <v>战役</v>
       </c>
-      <c r="D32" t="str">
-        <v>battle(战役)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>arrival</v>
       </c>
       <c r="B33" t="str">
-        <v>arrival</v>
+        <v>/əˈraɪvl/</v>
       </c>
       <c r="C33" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>到达</v>
       </c>
-      <c r="D33" t="str">
-        <v>arrival(到达)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>lady</v>
       </c>
       <c r="B34" t="str">
-        <v>lady</v>
+        <v>/ˈleɪdi/</v>
       </c>
       <c r="C34" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>女士</v>
       </c>
-      <c r="D34" t="str">
-        <v>lady(女士)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>Christian</v>
       </c>
       <c r="B35" t="str">
-        <v>Christian</v>
+        <v>/'krɪtʃən/</v>
       </c>
       <c r="C35" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D35" t="str">
         <v>基督徒</v>
       </c>
-      <c r="D35" t="str">
-        <v>Christian(基督徒)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>unconscious</v>
       </c>
       <c r="B36" t="str">
-        <v>unconscious</v>
+        <v>/ʌnˈkɑːnʃəs/</v>
       </c>
       <c r="C36" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D36" t="str">
         <v>无意识的</v>
       </c>
-      <c r="D36" t="str">
-        <v>unconscious(无意识的)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>fun</v>
       </c>
       <c r="B37" t="str">
-        <v>fun</v>
+        <v>/fʌn/</v>
       </c>
       <c r="C37" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D37" t="str">
         <v>娱乐</v>
       </c>
-      <c r="D37" t="str">
-        <v>fun(娱乐)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>indoors</v>
       </c>
       <c r="B38" t="str">
-        <v>indoors</v>
+        <v>/ˌɪnˈdɔːrz/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D38" t="str">
         <v>室内</v>
       </c>
-      <c r="D38" t="str">
-        <v>indoors(室内)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>utilize</v>
       </c>
       <c r="B39" t="str">
-        <v>utilize</v>
+        <v>/ˈjuːtəlaɪz/</v>
       </c>
       <c r="C39" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D39" t="str">
         <v>利用</v>
       </c>
-      <c r="D39" t="str">
-        <v>utilize(利用)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>kick</v>
       </c>
       <c r="B40" t="str">
-        <v>kick</v>
+        <v>/kɪk/</v>
       </c>
       <c r="C40" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D40" t="str">
         <v>踢</v>
       </c>
-      <c r="D40" t="str">
-        <v>kick(踢)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>tail</v>
       </c>
       <c r="B41" t="str">
-        <v>tail</v>
+        <v>/teɪl/</v>
       </c>
       <c r="C41" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D41" t="str">
         <v>尾巴</v>
       </c>
-      <c r="D41" t="str">
-        <v>tail(尾巴)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>nobody</v>
       </c>
       <c r="B42" t="str">
-        <v>nobody</v>
+        <v>/ˈnoʊbədi/</v>
       </c>
       <c r="C42" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D42" t="str">
         <v>没有人</v>
       </c>
-      <c r="D42" t="str">
-        <v>nobody(没有人)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>breast</v>
       </c>
       <c r="B43" t="str">
-        <v>breast</v>
+        <v>/brest/</v>
       </c>
       <c r="C43" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D43" t="str">
         <v>胸部</v>
       </c>
-      <c r="D43" t="str">
-        <v>breast(胸部)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>low</v>
       </c>
       <c r="B44" t="str">
-        <v>low</v>
+        <v>/loʊ/</v>
       </c>
       <c r="C44" t="str">
+        <v>n./vi./v./adj./adv.</v>
+      </c>
+      <c r="D44" t="str">
         <v>低下</v>
       </c>
-      <c r="D44" t="str">
-        <v>low(低下)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>pile</v>
       </c>
       <c r="B45" t="str">
-        <v>pile</v>
+        <v>/paɪl/</v>
       </c>
       <c r="C45" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D45" t="str">
         <v>堆</v>
       </c>
-      <c r="D45" t="str">
-        <v>pile(堆)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>specially</v>
       </c>
       <c r="B46" t="str">
-        <v>specially</v>
+        <v>/ˈspeʃəli/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D46" t="str">
         <v>专门</v>
       </c>
-      <c r="D46" t="str">
-        <v>specially(专门)📢</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>basketball</v>
       </c>
       <c r="B47" t="str">
-        <v>basketball</v>
+        <v>/ˈbæskɪtbɔːl/</v>
       </c>
       <c r="C47" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>篮球</v>
       </c>
-      <c r="D47" t="str">
-        <v>basketball(篮球)📢</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>stumble</v>
       </c>
       <c r="B48" t="str">
-        <v>stumble</v>
+        <v>/ˈstʌmbl/</v>
       </c>
       <c r="C48" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D48" t="str">
         <v>跌倒</v>
       </c>
-      <c r="D48" t="str">
-        <v>stumble(跌倒)📢</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>living</v>
       </c>
       <c r="B49" t="str">
-        <v>living</v>
+        <v>/ˈlɪvɪŋ/</v>
       </c>
       <c r="C49" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D49" t="str">
         <v>生活</v>
       </c>
-      <c r="D49" t="str">
-        <v>living(生活)📢</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>squirrel</v>
       </c>
       <c r="B50" t="str">
-        <v>squirrel</v>
+        <v>/ˈskwɜːrəl/</v>
       </c>
       <c r="C50" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D50" t="str">
         <v>松鼠</v>
       </c>
-      <c r="D50" t="str">
-        <v>squirrel(松鼠)📢</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>feast</v>
       </c>
       <c r="B51" t="str">
-        <v>feast</v>
+        <v>/fiːst/</v>
       </c>
       <c r="C51" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D51" t="str">
         <v>盛宴</v>
-      </c>
-      <c r="D51" t="str">
-        <v>feast(盛宴)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>southwest</v>
-      </c>
-      <c r="C52" t="str">
-        <v>西南</v>
-      </c>
-      <c r="D52" t="str">
-        <v>southwest(西南)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>throne</v>
-      </c>
-      <c r="C53" t="str">
-        <v>王座</v>
-      </c>
-      <c r="D53" t="str">
-        <v>throne(王座)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>